--- a/artfynd/A 26474-2026 artfynd.xlsx
+++ b/artfynd/A 26474-2026 artfynd.xlsx
@@ -798,7 +798,7 @@
         <v>136648520</v>
       </c>
       <c r="B3" t="n">
-        <v>92102</v>
+        <v>92105</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 26474-2026 artfynd.xlsx
+++ b/artfynd/A 26474-2026 artfynd.xlsx
@@ -798,7 +798,7 @@
         <v>136648520</v>
       </c>
       <c r="B3" t="n">
-        <v>92105</v>
+        <v>92106</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 26474-2026 artfynd.xlsx
+++ b/artfynd/A 26474-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136648513</v>
       </c>
       <c r="B2" t="n">
-        <v>80452</v>
+        <v>80454</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>136648520</v>
       </c>
       <c r="B3" t="n">
-        <v>92106</v>
+        <v>92111</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -913,7 +913,7 @@
         <v>136648514</v>
       </c>
       <c r="B4" t="n">
-        <v>80589</v>
+        <v>80591</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>136648515</v>
       </c>
       <c r="B5" t="n">
-        <v>80589</v>
+        <v>80591</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1143,7 +1143,7 @@
         <v>136648518</v>
       </c>
       <c r="B6" t="n">
-        <v>80594</v>
+        <v>80596</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 26474-2026 artfynd.xlsx
+++ b/artfynd/A 26474-2026 artfynd.xlsx
@@ -798,7 +798,7 @@
         <v>136648520</v>
       </c>
       <c r="B3" t="n">
-        <v>92111</v>
+        <v>92113</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 26474-2026 artfynd.xlsx
+++ b/artfynd/A 26474-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136648513</v>
       </c>
       <c r="B2" t="n">
-        <v>80454</v>
+        <v>80458</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>136648520</v>
       </c>
       <c r="B3" t="n">
-        <v>92113</v>
+        <v>92115</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -913,7 +913,7 @@
         <v>136648514</v>
       </c>
       <c r="B4" t="n">
-        <v>80591</v>
+        <v>80595</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>136648515</v>
       </c>
       <c r="B5" t="n">
-        <v>80591</v>
+        <v>80595</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1143,7 +1143,7 @@
         <v>136648518</v>
       </c>
       <c r="B6" t="n">
-        <v>80596</v>
+        <v>80600</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 26474-2026 artfynd.xlsx
+++ b/artfynd/A 26474-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136648513</v>
       </c>
       <c r="B2" t="n">
-        <v>80458</v>
+        <v>80460</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>136648520</v>
       </c>
       <c r="B3" t="n">
-        <v>92115</v>
+        <v>92117</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -913,7 +913,7 @@
         <v>136648514</v>
       </c>
       <c r="B4" t="n">
-        <v>80595</v>
+        <v>80597</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>136648515</v>
       </c>
       <c r="B5" t="n">
-        <v>80595</v>
+        <v>80597</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1143,7 +1143,7 @@
         <v>136648518</v>
       </c>
       <c r="B6" t="n">
-        <v>80600</v>
+        <v>80602</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 26474-2026 artfynd.xlsx
+++ b/artfynd/A 26474-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136648513</v>
       </c>
       <c r="B2" t="n">
-        <v>80460</v>
+        <v>80461</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>136648520</v>
       </c>
       <c r="B3" t="n">
-        <v>92117</v>
+        <v>92118</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -913,7 +913,7 @@
         <v>136648514</v>
       </c>
       <c r="B4" t="n">
-        <v>80597</v>
+        <v>80598</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>136648515</v>
       </c>
       <c r="B5" t="n">
-        <v>80597</v>
+        <v>80598</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1143,7 +1143,7 @@
         <v>136648518</v>
       </c>
       <c r="B6" t="n">
-        <v>80602</v>
+        <v>80603</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 26474-2026 artfynd.xlsx
+++ b/artfynd/A 26474-2026 artfynd.xlsx
@@ -798,7 +798,7 @@
         <v>136648520</v>
       </c>
       <c r="B3" t="n">
-        <v>92118</v>
+        <v>92124</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 26474-2026 artfynd.xlsx
+++ b/artfynd/A 26474-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136648513</v>
       </c>
       <c r="B2" t="n">
-        <v>80461</v>
+        <v>80463</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>136648520</v>
       </c>
       <c r="B3" t="n">
-        <v>92124</v>
+        <v>92128</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -913,7 +913,7 @@
         <v>136648514</v>
       </c>
       <c r="B4" t="n">
-        <v>80598</v>
+        <v>80600</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>136648515</v>
       </c>
       <c r="B5" t="n">
-        <v>80598</v>
+        <v>80600</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1143,7 +1143,7 @@
         <v>136648518</v>
       </c>
       <c r="B6" t="n">
-        <v>80603</v>
+        <v>80605</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 26474-2026 artfynd.xlsx
+++ b/artfynd/A 26474-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136648513</v>
       </c>
       <c r="B2" t="n">
-        <v>80463</v>
+        <v>80466</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>136648520</v>
       </c>
       <c r="B3" t="n">
-        <v>92128</v>
+        <v>92130</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -913,7 +913,7 @@
         <v>136648514</v>
       </c>
       <c r="B4" t="n">
-        <v>80600</v>
+        <v>80603</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>136648515</v>
       </c>
       <c r="B5" t="n">
-        <v>80600</v>
+        <v>80603</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1143,7 +1143,7 @@
         <v>136648518</v>
       </c>
       <c r="B6" t="n">
-        <v>80605</v>
+        <v>80608</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 26474-2026 artfynd.xlsx
+++ b/artfynd/A 26474-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136648513</v>
       </c>
       <c r="B2" t="n">
-        <v>80466</v>
+        <v>80479</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>136648520</v>
       </c>
       <c r="B3" t="n">
-        <v>92130</v>
+        <v>92143</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -913,7 +913,7 @@
         <v>136648514</v>
       </c>
       <c r="B4" t="n">
-        <v>80603</v>
+        <v>80616</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>136648515</v>
       </c>
       <c r="B5" t="n">
-        <v>80603</v>
+        <v>80616</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1143,7 +1143,7 @@
         <v>136648518</v>
       </c>
       <c r="B6" t="n">
-        <v>80608</v>
+        <v>80621</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 26474-2026 artfynd.xlsx
+++ b/artfynd/A 26474-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136648513</v>
       </c>
       <c r="B2" t="n">
-        <v>80479</v>
+        <v>80481</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>136648520</v>
       </c>
       <c r="B3" t="n">
-        <v>92143</v>
+        <v>92145</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -913,7 +913,7 @@
         <v>136648514</v>
       </c>
       <c r="B4" t="n">
-        <v>80616</v>
+        <v>80618</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>136648515</v>
       </c>
       <c r="B5" t="n">
-        <v>80616</v>
+        <v>80618</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1143,7 +1143,7 @@
         <v>136648518</v>
       </c>
       <c r="B6" t="n">
-        <v>80621</v>
+        <v>80623</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
